--- a/BackEnd/Excels/matricula_inicial.xlsx
+++ b/BackEnd/Excels/matricula_inicial.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josue\Downloads\Formatos excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josue\Programacion\HerramientaDeServicio-main (1)\HerramientaDeServicio-main\BackEnd\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A255D50E-32B7-421C-9082-8AF92AC1470C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3775E0-2E8F-4ECA-8C9F-762FBA2AFC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="468" xr2:uid="{B0175210-878E-4884-BA88-51C047AB31BC}"/>
   </bookViews>
@@ -16,22 +16,11 @@
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="145621"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="87">
   <si>
     <t>MATRICULA INICIAL(Preescolar, I y II Etapa Educación Básica)</t>
   </si>
@@ -276,18 +265,6 @@
     <t>OD 05490813</t>
   </si>
   <si>
-    <t>Grado: Maternal</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>N° de Alumnos en la Sección: 18</t>
-  </si>
-  <si>
-    <t>N° de Alumnos en esta Página: 18</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -295,6 +272,15 @@
   </si>
   <si>
     <t>V- 11674933</t>
+  </si>
+  <si>
+    <t>N° de Alumnos en la Sección:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° de Alumnos en esta Página: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grado: </t>
   </si>
 </sst>
 </file>
@@ -302,8 +288,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="170" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00&quot; €&quot;_-;\-* #,##0.00&quot; €&quot;_-;_-* \-??&quot; €&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -962,8 +948,8 @@
     <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="30" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="33" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
@@ -975,12 +961,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1">
@@ -1013,23 +999,23 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="2" borderId="0" xfId="31" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="31" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection hidden="1"/>
     </xf>
@@ -1037,11 +1023,8 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1055,7 +1038,7 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1067,7 +1050,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1075,13 +1058,168 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1096,6 +1234,70 @@
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1155,244 +1357,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1927,25 +1891,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
       <c r="H1" s="11"/>
-      <c r="I1" s="94" t="s">
+      <c r="I1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="C2" s="12"/>
@@ -1955,16 +1919,16 @@
       <c r="G2" s="12"/>
       <c r="H2" s="13"/>
       <c r="J2" s="11"/>
-      <c r="K2" s="109" t="s">
+      <c r="K2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="109"/>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="109"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
       <c r="S2" s="11"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1976,17 +1940,17 @@
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
       <c r="J3" s="11"/>
-      <c r="K3" s="81" t="s">
+      <c r="K3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="103" t="s">
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="O3" s="103"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
       <c r="R3" s="15"/>
       <c r="S3" s="15"/>
     </row>
@@ -2007,51 +1971,51 @@
       <c r="O4" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
     </row>
     <row r="5" spans="1:19" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-      <c r="Q5" s="81"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="41" t="s">
+      <c r="A6" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42" t="s">
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="96" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="29" t="s">
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
       <c r="K6" s="15" t="s">
         <v>75</v>
       </c>
@@ -2065,68 +2029,68 @@
         <v>4</v>
       </c>
       <c r="S6" s="18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="81" t="s">
+      <c r="A7" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="106" t="s">
+      <c r="B7" s="30"/>
+      <c r="C7" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="107" t="s">
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="M7" s="107"/>
-      <c r="N7" s="103" t="s">
+      <c r="M7" s="30"/>
+      <c r="N7" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="O7" s="103"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="103"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="32"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="81"/>
-      <c r="C8" s="103" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="104" t="s">
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="104"/>
-      <c r="H8" s="103" t="s">
+      <c r="G8" s="36"/>
+      <c r="H8" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="I8" s="103"/>
-      <c r="J8" s="103"/>
-      <c r="K8" s="103"/>
-      <c r="L8" s="94" t="s">
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="94"/>
-      <c r="N8" s="94"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="105"/>
-      <c r="Q8" s="105"/>
-      <c r="R8" s="105"/>
-      <c r="S8" s="105"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
@@ -2137,995 +2101,983 @@
       <c r="D9" s="19"/>
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="94" t="s">
+      <c r="A10" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="94"/>
-      <c r="F10" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="95" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="96" t="s">
+      <c r="E10" s="34"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
-      <c r="S10" s="26"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="N10" s="39"/>
+      <c r="O10" s="39"/>
+      <c r="P10" s="39"/>
+      <c r="Q10" s="39"/>
+      <c r="R10" s="39"/>
+      <c r="S10" s="25"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="81" t="s">
+      <c r="A11" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="81"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="97" t="s">
+      <c r="A12" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="99"/>
-      <c r="D12" s="102" t="s">
+      <c r="C12" s="43"/>
+      <c r="D12" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="102" t="s">
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="102"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="102"/>
-      <c r="N12" s="90" t="s">
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="O12" s="92" t="s">
+      <c r="O12" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="92"/>
-      <c r="Q12" s="92"/>
-      <c r="R12" s="92" t="s">
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="S12" s="92"/>
+      <c r="S12" s="40"/>
     </row>
     <row r="13" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="97"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="102"/>
-      <c r="I13" s="102"/>
-      <c r="J13" s="102"/>
-      <c r="K13" s="102"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="102"/>
-      <c r="N13" s="91"/>
-      <c r="O13" s="22" t="s">
+      <c r="A13" s="41"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="P13" s="22" t="s">
+      <c r="P13" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="Q13" s="22" t="s">
+      <c r="Q13" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="22" t="s">
+      <c r="R13" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="S13" s="22" t="s">
+      <c r="S13" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="85"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="87"/>
-      <c r="E14" s="88"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="87"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="88"/>
-      <c r="L14" s="88"/>
-      <c r="M14" s="89"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
     </row>
     <row r="15" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="87"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="88"/>
-      <c r="L15" s="88"/>
-      <c r="M15" s="89"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
     </row>
     <row r="16" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="85"/>
-      <c r="C16" s="86"/>
-      <c r="D16" s="87"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="87"/>
-      <c r="J16" s="88"/>
-      <c r="K16" s="88"/>
-      <c r="L16" s="88"/>
-      <c r="M16" s="89"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="53"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
     </row>
     <row r="17" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="88"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="87"/>
-      <c r="J17" s="88"/>
-      <c r="K17" s="88"/>
-      <c r="L17" s="88"/>
-      <c r="M17" s="89"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="27"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="53"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="26"/>
     </row>
     <row r="18" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="85"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="88"/>
-      <c r="L18" s="88"/>
-      <c r="M18" s="89"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="27"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="53"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="26"/>
     </row>
     <row r="19" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="88"/>
-      <c r="M19" s="89"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="25"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="27"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="26"/>
     </row>
     <row r="20" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="85"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="88"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="87"/>
-      <c r="J20" s="88"/>
-      <c r="K20" s="88"/>
-      <c r="L20" s="88"/>
-      <c r="M20" s="89"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="27"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="52"/>
+      <c r="M20" s="53"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="23"/>
+      <c r="S20" s="26"/>
     </row>
     <row r="21" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="85"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="87"/>
-      <c r="J21" s="88"/>
-      <c r="K21" s="88"/>
-      <c r="L21" s="88"/>
-      <c r="M21" s="89"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="27"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="26"/>
     </row>
     <row r="22" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="85"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="87"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="88"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="87"/>
-      <c r="J22" s="88"/>
-      <c r="K22" s="88"/>
-      <c r="L22" s="88"/>
-      <c r="M22" s="89"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="27"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="53"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="26"/>
     </row>
     <row r="23" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="85"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="87"/>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88"/>
-      <c r="M23" s="89"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="27"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="26"/>
     </row>
     <row r="24" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="85"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
-      <c r="M24" s="89"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="25"/>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="27"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="53"/>
+      <c r="N24" s="24"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="24"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="26"/>
     </row>
     <row r="25" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="85"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="88"/>
-      <c r="K25" s="88"/>
-      <c r="L25" s="88"/>
-      <c r="M25" s="89"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
-      <c r="P25" s="25"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="24"/>
-      <c r="S25" s="27"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="23"/>
+      <c r="S25" s="26"/>
     </row>
     <row r="26" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="85"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="88"/>
-      <c r="L26" s="88"/>
-      <c r="M26" s="89"/>
-      <c r="N26" s="25"/>
-      <c r="O26" s="25"/>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="24"/>
-      <c r="S26" s="27"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="26"/>
     </row>
     <row r="27" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="85"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
-      <c r="L27" s="88"/>
-      <c r="M27" s="89"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="24"/>
-      <c r="S27" s="27"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="26"/>
     </row>
     <row r="28" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="85"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="87"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="88"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="87"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="89"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="27"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="26"/>
     </row>
     <row r="29" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="85"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="24"/>
-      <c r="S29" s="27"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="26"/>
     </row>
     <row r="30" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="85"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="87"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="25"/>
-      <c r="P30" s="25"/>
-      <c r="Q30" s="25"/>
-      <c r="R30" s="24"/>
-      <c r="S30" s="27"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="53"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="24"/>
+      <c r="R30" s="23"/>
+      <c r="S30" s="26"/>
     </row>
     <row r="31" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="85"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="87"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="87"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="89"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="25"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="24"/>
-      <c r="S31" s="27"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="26"/>
     </row>
     <row r="32" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="85"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="87"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="88"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="88"/>
-      <c r="K32" s="88"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="89"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="24"/>
-      <c r="S32" s="27"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="53"/>
+      <c r="N32" s="24"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
+      <c r="Q32" s="24"/>
+      <c r="R32" s="23"/>
+      <c r="S32" s="26"/>
     </row>
     <row r="33" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="85"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="89"/>
-      <c r="N33" s="25"/>
-      <c r="O33" s="25"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
-      <c r="R33" s="24"/>
-      <c r="S33" s="27"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24"/>
+      <c r="Q33" s="24"/>
+      <c r="R33" s="23"/>
+      <c r="S33" s="26"/>
     </row>
     <row r="34" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="85"/>
-      <c r="C34" s="86"/>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="87"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="89"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="24"/>
-      <c r="S34" s="27"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+      <c r="Q34" s="24"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="26"/>
     </row>
     <row r="35" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="85"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="87"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
-      <c r="G35" s="88"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="87"/>
-      <c r="J35" s="88"/>
-      <c r="K35" s="88"/>
-      <c r="L35" s="88"/>
-      <c r="M35" s="89"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="24"/>
-      <c r="S35" s="27"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="26"/>
     </row>
     <row r="36" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B36" s="83"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="84"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="84"/>
-      <c r="J36" s="58"/>
-      <c r="K36" s="58"/>
-      <c r="L36" s="58"/>
-      <c r="M36" s="59"/>
-      <c r="N36" s="25"/>
-      <c r="O36" s="25"/>
-      <c r="P36" s="25"/>
-      <c r="Q36" s="25"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="27"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="24"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="24"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="26"/>
     </row>
     <row r="37" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="83"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="84"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="84"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="58"/>
-      <c r="L37" s="58"/>
-      <c r="M37" s="59"/>
-      <c r="N37" s="25"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="25"/>
-      <c r="Q37" s="25"/>
-      <c r="R37" s="24"/>
-      <c r="S37" s="27"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="55"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="24"/>
+      <c r="R37" s="23"/>
+      <c r="S37" s="26"/>
     </row>
     <row r="38" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="83"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="84"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="84"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="58"/>
-      <c r="L38" s="58"/>
-      <c r="M38" s="59"/>
-      <c r="N38" s="25"/>
-      <c r="O38" s="25"/>
-      <c r="P38" s="25"/>
-      <c r="Q38" s="25"/>
-      <c r="R38" s="24"/>
-      <c r="S38" s="27"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="55"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="26"/>
     </row>
     <row r="39" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="83"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="84"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="59"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="58"/>
-      <c r="K39" s="58"/>
-      <c r="L39" s="58"/>
-      <c r="M39" s="59"/>
-      <c r="N39" s="25"/>
-      <c r="O39" s="25"/>
-      <c r="P39" s="25"/>
-      <c r="Q39" s="25"/>
-      <c r="R39" s="24"/>
-      <c r="S39" s="27"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="55"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="24"/>
+      <c r="R39" s="23"/>
+      <c r="S39" s="26"/>
     </row>
     <row r="40" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="83"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="84"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="84"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="59"/>
-      <c r="N40" s="25"/>
-      <c r="O40" s="25"/>
-      <c r="P40" s="25"/>
-      <c r="Q40" s="25"/>
-      <c r="R40" s="24"/>
-      <c r="S40" s="27"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="55"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="26"/>
     </row>
     <row r="41" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B41" s="83"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="84"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="59"/>
-      <c r="N41" s="25"/>
-      <c r="O41" s="25"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="25"/>
-      <c r="R41" s="24"/>
-      <c r="S41" s="27"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="57"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="24"/>
+      <c r="Q41" s="24"/>
+      <c r="R41" s="23"/>
+      <c r="S41" s="26"/>
     </row>
     <row r="42" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="55"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="58"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="58"/>
-      <c r="M42" s="59"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="28"/>
-      <c r="R42" s="27"/>
-      <c r="S42" s="27"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="55"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="27"/>
+      <c r="P42" s="27"/>
+      <c r="Q42" s="27"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="26"/>
     </row>
     <row r="43" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="57"/>
-      <c r="J43" s="58"/>
-      <c r="K43" s="58"/>
-      <c r="L43" s="58"/>
-      <c r="M43" s="59"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="55"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="27"/>
+      <c r="P43" s="27"/>
+      <c r="Q43" s="27"/>
+      <c r="R43" s="26"/>
+      <c r="S43" s="26"/>
     </row>
     <row r="44" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="56"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="57"/>
-      <c r="J44" s="58"/>
-      <c r="K44" s="58"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="59"/>
-      <c r="N44" s="27"/>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="27"/>
-      <c r="S44" s="27"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="55"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="55"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="27"/>
+      <c r="Q44" s="27"/>
+      <c r="R44" s="26"/>
+      <c r="S44" s="26"/>
     </row>
     <row r="45" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="B45" s="55"/>
-      <c r="C45" s="56"/>
-      <c r="D45" s="57"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="57"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="58"/>
-      <c r="L45" s="58"/>
-      <c r="M45" s="59"/>
-      <c r="N45" s="27"/>
-      <c r="O45" s="28"/>
-      <c r="P45" s="28"/>
-      <c r="Q45" s="28"/>
-      <c r="R45" s="27"/>
-      <c r="S45" s="27"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="57"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="55"/>
+      <c r="N45" s="26"/>
+      <c r="O45" s="27"/>
+      <c r="P45" s="27"/>
+      <c r="Q45" s="27"/>
+      <c r="R45" s="26"/>
+      <c r="S45" s="26"/>
     </row>
     <row r="46" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="55"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="57"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="59"/>
-      <c r="I46" s="57"/>
-      <c r="J46" s="58"/>
-      <c r="K46" s="58"/>
-      <c r="L46" s="58"/>
-      <c r="M46" s="59"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="55"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="57"/>
+      <c r="L46" s="57"/>
+      <c r="M46" s="55"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="27"/>
+      <c r="P46" s="27"/>
+      <c r="Q46" s="27"/>
+      <c r="R46" s="26"/>
+      <c r="S46" s="26"/>
     </row>
     <row r="47" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B47" s="55"/>
-      <c r="C47" s="56"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="57"/>
-      <c r="J47" s="58"/>
-      <c r="K47" s="58"/>
-      <c r="L47" s="58"/>
-      <c r="M47" s="59"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="28"/>
-      <c r="P47" s="28"/>
-      <c r="Q47" s="28"/>
-      <c r="R47" s="27"/>
-      <c r="S47" s="27"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="57"/>
+      <c r="L47" s="57"/>
+      <c r="M47" s="55"/>
+      <c r="N47" s="26"/>
+      <c r="O47" s="27"/>
+      <c r="P47" s="27"/>
+      <c r="Q47" s="27"/>
+      <c r="R47" s="26"/>
+      <c r="S47" s="26"/>
     </row>
     <row r="48" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B48" s="55"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="57"/>
-      <c r="J48" s="58"/>
-      <c r="K48" s="58"/>
-      <c r="L48" s="58"/>
-      <c r="M48" s="59"/>
-      <c r="N48" s="27"/>
-      <c r="O48" s="28"/>
-      <c r="P48" s="28"/>
-      <c r="Q48" s="28"/>
-      <c r="R48" s="27"/>
-      <c r="S48" s="27"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="58"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="57"/>
+      <c r="L48" s="57"/>
+      <c r="M48" s="55"/>
+      <c r="N48" s="26"/>
+      <c r="O48" s="27"/>
+      <c r="P48" s="27"/>
+      <c r="Q48" s="27"/>
+      <c r="R48" s="26"/>
+      <c r="S48" s="26"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A49" s="81" t="s">
+      <c r="A49" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="B49" s="81"/>
-      <c r="C49" s="81"/>
-      <c r="D49" s="82"/>
-      <c r="E49" s="82"/>
-      <c r="F49" s="82"/>
-      <c r="G49" s="82"/>
-      <c r="H49" s="82"/>
-      <c r="I49" s="82"/>
-      <c r="J49" s="82"/>
-      <c r="K49" s="82"/>
-      <c r="L49" s="82"/>
-      <c r="M49" s="82"/>
-      <c r="N49" s="82"/>
-      <c r="O49" s="82"/>
-      <c r="P49" s="82"/>
-      <c r="Q49" s="82"/>
-      <c r="R49" s="82"/>
-      <c r="S49" s="82"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73"/>
+      <c r="J49" s="73"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="73"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="73"/>
+      <c r="O49" s="73"/>
+      <c r="P49" s="73"/>
+      <c r="Q49" s="73"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="73"/>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A50" s="67"/>
-      <c r="B50" s="67"/>
-      <c r="C50" s="67"/>
-      <c r="D50" s="67"/>
-      <c r="E50" s="67"/>
-      <c r="F50" s="67"/>
-      <c r="G50" s="67"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="67"/>
-      <c r="J50" s="67"/>
-      <c r="K50" s="67"/>
-      <c r="L50" s="67"/>
-      <c r="M50" s="67"/>
-      <c r="N50" s="67"/>
-      <c r="O50" s="67"/>
-      <c r="P50" s="67"/>
-      <c r="Q50" s="67"/>
-      <c r="R50" s="67"/>
-      <c r="S50" s="67"/>
+      <c r="A50" s="59"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="59"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="59"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="59"/>
+      <c r="K50" s="59"/>
+      <c r="L50" s="59"/>
+      <c r="M50" s="59"/>
+      <c r="N50" s="59"/>
+      <c r="O50" s="59"/>
+      <c r="P50" s="59"/>
+      <c r="Q50" s="59"/>
+      <c r="R50" s="59"/>
+      <c r="S50" s="59"/>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A51" s="67"/>
-      <c r="B51" s="67"/>
-      <c r="C51" s="67"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
-      <c r="F51" s="67"/>
-      <c r="G51" s="67"/>
-      <c r="H51" s="67"/>
-      <c r="I51" s="67"/>
-      <c r="J51" s="67"/>
-      <c r="K51" s="67"/>
-      <c r="L51" s="67"/>
-      <c r="M51" s="67"/>
-      <c r="N51" s="67"/>
-      <c r="O51" s="67"/>
-      <c r="P51" s="67"/>
-      <c r="Q51" s="67"/>
-      <c r="R51" s="67"/>
-      <c r="S51" s="67"/>
+      <c r="A51" s="59"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="59"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="59"/>
+      <c r="F51" s="59"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="59"/>
+      <c r="K51" s="59"/>
+      <c r="L51" s="59"/>
+      <c r="M51" s="59"/>
+      <c r="N51" s="59"/>
+      <c r="O51" s="59"/>
+      <c r="P51" s="59"/>
+      <c r="Q51" s="59"/>
+      <c r="R51" s="59"/>
+      <c r="S51" s="59"/>
     </row>
     <row r="52" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
@@ -3134,11 +3086,11 @@
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="69"/>
-      <c r="G52" s="69"/>
-      <c r="H52" s="69"/>
-      <c r="I52" s="70"/>
+      <c r="E52" s="86"/>
+      <c r="F52" s="87"/>
+      <c r="G52" s="87"/>
+      <c r="H52" s="87"/>
+      <c r="I52" s="88"/>
       <c r="K52" s="1" t="s">
         <v>59</v>
       </c>
@@ -3146,331 +3098,281 @@
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
-      <c r="P52" s="68"/>
-      <c r="Q52" s="69"/>
-      <c r="R52" s="69"/>
-      <c r="S52" s="70"/>
+      <c r="P52" s="86"/>
+      <c r="Q52" s="87"/>
+      <c r="R52" s="87"/>
+      <c r="S52" s="88"/>
     </row>
     <row r="53" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="71" t="s">
+      <c r="A53" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="B53" s="71"/>
-      <c r="C53" s="71"/>
-      <c r="D53" s="71"/>
-      <c r="E53" s="72" t="s">
+      <c r="B53" s="60"/>
+      <c r="C53" s="60"/>
+      <c r="D53" s="60"/>
+      <c r="E53" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="F53" s="73"/>
-      <c r="G53" s="73"/>
-      <c r="H53" s="73"/>
-      <c r="I53" s="74"/>
-      <c r="K53" s="71" t="s">
+      <c r="F53" s="62"/>
+      <c r="G53" s="62"/>
+      <c r="H53" s="62"/>
+      <c r="I53" s="63"/>
+      <c r="K53" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="L53" s="71"/>
-      <c r="M53" s="71"/>
-      <c r="N53" s="71"/>
-      <c r="O53" s="71"/>
-      <c r="P53" s="72" t="s">
+      <c r="L53" s="60"/>
+      <c r="M53" s="60"/>
+      <c r="N53" s="60"/>
+      <c r="O53" s="60"/>
+      <c r="P53" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="Q53" s="73"/>
-      <c r="R53" s="73"/>
-      <c r="S53" s="74"/>
+      <c r="Q53" s="62"/>
+      <c r="R53" s="62"/>
+      <c r="S53" s="63"/>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A54" s="32" t="s">
+      <c r="A54" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="75"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="76"/>
-      <c r="H54" s="76"/>
-      <c r="I54" s="77"/>
-      <c r="K54" s="32" t="s">
+      <c r="B54" s="71"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="65"/>
+      <c r="G54" s="65"/>
+      <c r="H54" s="65"/>
+      <c r="I54" s="66"/>
+      <c r="K54" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="L54" s="33"/>
-      <c r="M54" s="33"/>
-      <c r="N54" s="33"/>
-      <c r="O54" s="34"/>
-      <c r="P54" s="75"/>
-      <c r="Q54" s="76"/>
-      <c r="R54" s="76"/>
-      <c r="S54" s="77"/>
+      <c r="L54" s="71"/>
+      <c r="M54" s="71"/>
+      <c r="N54" s="71"/>
+      <c r="O54" s="72"/>
+      <c r="P54" s="64"/>
+      <c r="Q54" s="65"/>
+      <c r="R54" s="65"/>
+      <c r="S54" s="66"/>
     </row>
     <row r="55" spans="1:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="B55" s="44"/>
-      <c r="C55" s="44"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="75"/>
-      <c r="F55" s="76"/>
-      <c r="G55" s="76"/>
-      <c r="H55" s="76"/>
-      <c r="I55" s="77"/>
-      <c r="K55" s="49"/>
-      <c r="L55" s="50"/>
-      <c r="M55" s="50"/>
-      <c r="N55" s="50"/>
-      <c r="O55" s="51"/>
-      <c r="P55" s="75"/>
-      <c r="Q55" s="76"/>
-      <c r="R55" s="76"/>
-      <c r="S55" s="77"/>
+      <c r="A55" s="97" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" s="98"/>
+      <c r="C55" s="98"/>
+      <c r="D55" s="99"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="65"/>
+      <c r="G55" s="65"/>
+      <c r="H55" s="65"/>
+      <c r="I55" s="66"/>
+      <c r="K55" s="103"/>
+      <c r="L55" s="81"/>
+      <c r="M55" s="81"/>
+      <c r="N55" s="81"/>
+      <c r="O55" s="82"/>
+      <c r="P55" s="64"/>
+      <c r="Q55" s="65"/>
+      <c r="R55" s="65"/>
+      <c r="S55" s="66"/>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
-      <c r="B56" s="47"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="76"/>
-      <c r="G56" s="76"/>
-      <c r="H56" s="76"/>
-      <c r="I56" s="77"/>
-      <c r="K56" s="52"/>
-      <c r="L56" s="53"/>
-      <c r="M56" s="53"/>
-      <c r="N56" s="53"/>
-      <c r="O56" s="54"/>
-      <c r="P56" s="75"/>
-      <c r="Q56" s="76"/>
-      <c r="R56" s="76"/>
-      <c r="S56" s="77"/>
+      <c r="A56" s="100"/>
+      <c r="B56" s="101"/>
+      <c r="C56" s="101"/>
+      <c r="D56" s="102"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="65"/>
+      <c r="H56" s="65"/>
+      <c r="I56" s="66"/>
+      <c r="K56" s="83"/>
+      <c r="L56" s="84"/>
+      <c r="M56" s="84"/>
+      <c r="N56" s="84"/>
+      <c r="O56" s="85"/>
+      <c r="P56" s="64"/>
+      <c r="Q56" s="65"/>
+      <c r="R56" s="65"/>
+      <c r="S56" s="66"/>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A57" s="32" t="s">
+      <c r="A57" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="B57" s="33"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="75"/>
-      <c r="F57" s="76"/>
-      <c r="G57" s="76"/>
-      <c r="H57" s="76"/>
-      <c r="I57" s="77"/>
-      <c r="K57" s="32" t="s">
+      <c r="B57" s="71"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="66"/>
+      <c r="K57" s="70" t="s">
         <v>63</v>
       </c>
-      <c r="L57" s="33"/>
-      <c r="M57" s="33"/>
-      <c r="N57" s="33"/>
-      <c r="O57" s="34"/>
-      <c r="P57" s="75"/>
-      <c r="Q57" s="76"/>
-      <c r="R57" s="76"/>
-      <c r="S57" s="77"/>
+      <c r="L57" s="71"/>
+      <c r="M57" s="71"/>
+      <c r="N57" s="71"/>
+      <c r="O57" s="72"/>
+      <c r="P57" s="64"/>
+      <c r="Q57" s="65"/>
+      <c r="R57" s="65"/>
+      <c r="S57" s="66"/>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A58" s="60" t="s">
-        <v>87</v>
-      </c>
-      <c r="B58" s="61"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="62"/>
-      <c r="E58" s="75"/>
-      <c r="F58" s="76"/>
-      <c r="G58" s="76"/>
-      <c r="H58" s="76"/>
-      <c r="I58" s="77"/>
-      <c r="K58" s="66"/>
-      <c r="L58" s="50"/>
-      <c r="M58" s="50"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="51"/>
-      <c r="P58" s="75"/>
-      <c r="Q58" s="76"/>
-      <c r="R58" s="76"/>
-      <c r="S58" s="77"/>
+      <c r="A58" s="74" t="s">
+        <v>83</v>
+      </c>
+      <c r="B58" s="75"/>
+      <c r="C58" s="75"/>
+      <c r="D58" s="76"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="65"/>
+      <c r="H58" s="65"/>
+      <c r="I58" s="66"/>
+      <c r="K58" s="80"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="81"/>
+      <c r="N58" s="81"/>
+      <c r="O58" s="82"/>
+      <c r="P58" s="64"/>
+      <c r="Q58" s="65"/>
+      <c r="R58" s="65"/>
+      <c r="S58" s="66"/>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A59" s="63"/>
-      <c r="B59" s="64"/>
-      <c r="C59" s="64"/>
-      <c r="D59" s="65"/>
-      <c r="E59" s="75"/>
-      <c r="F59" s="76"/>
-      <c r="G59" s="76"/>
-      <c r="H59" s="76"/>
-      <c r="I59" s="77"/>
-      <c r="K59" s="52"/>
-      <c r="L59" s="53"/>
-      <c r="M59" s="53"/>
-      <c r="N59" s="53"/>
-      <c r="O59" s="54"/>
-      <c r="P59" s="75"/>
-      <c r="Q59" s="76"/>
-      <c r="R59" s="76"/>
-      <c r="S59" s="77"/>
+      <c r="A59" s="77"/>
+      <c r="B59" s="78"/>
+      <c r="C59" s="78"/>
+      <c r="D59" s="79"/>
+      <c r="E59" s="64"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="65"/>
+      <c r="H59" s="65"/>
+      <c r="I59" s="66"/>
+      <c r="K59" s="83"/>
+      <c r="L59" s="84"/>
+      <c r="M59" s="84"/>
+      <c r="N59" s="84"/>
+      <c r="O59" s="85"/>
+      <c r="P59" s="64"/>
+      <c r="Q59" s="65"/>
+      <c r="R59" s="65"/>
+      <c r="S59" s="66"/>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A60" s="32" t="s">
+      <c r="A60" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="75"/>
-      <c r="F60" s="76"/>
-      <c r="G60" s="76"/>
-      <c r="H60" s="76"/>
-      <c r="I60" s="77"/>
-      <c r="K60" s="32" t="s">
+      <c r="B60" s="71"/>
+      <c r="C60" s="71"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="64"/>
+      <c r="F60" s="65"/>
+      <c r="G60" s="65"/>
+      <c r="H60" s="65"/>
+      <c r="I60" s="66"/>
+      <c r="K60" s="70" t="s">
         <v>64</v>
       </c>
-      <c r="L60" s="33"/>
-      <c r="M60" s="33"/>
-      <c r="N60" s="33"/>
-      <c r="O60" s="34"/>
-      <c r="P60" s="75"/>
-      <c r="Q60" s="76"/>
-      <c r="R60" s="76"/>
-      <c r="S60" s="77"/>
+      <c r="L60" s="71"/>
+      <c r="M60" s="71"/>
+      <c r="N60" s="71"/>
+      <c r="O60" s="72"/>
+      <c r="P60" s="64"/>
+      <c r="Q60" s="65"/>
+      <c r="R60" s="65"/>
+      <c r="S60" s="66"/>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="6"/>
-      <c r="E61" s="75"/>
-      <c r="F61" s="76"/>
-      <c r="G61" s="76"/>
-      <c r="H61" s="76"/>
-      <c r="I61" s="77"/>
-      <c r="K61" s="35"/>
-      <c r="L61" s="36"/>
-      <c r="M61" s="36"/>
-      <c r="N61" s="36"/>
-      <c r="O61" s="37"/>
-      <c r="P61" s="75"/>
-      <c r="Q61" s="76"/>
-      <c r="R61" s="76"/>
-      <c r="S61" s="77"/>
+      <c r="E61" s="64"/>
+      <c r="F61" s="65"/>
+      <c r="G61" s="65"/>
+      <c r="H61" s="65"/>
+      <c r="I61" s="66"/>
+      <c r="K61" s="89"/>
+      <c r="L61" s="90"/>
+      <c r="M61" s="90"/>
+      <c r="N61" s="90"/>
+      <c r="O61" s="91"/>
+      <c r="P61" s="64"/>
+      <c r="Q61" s="65"/>
+      <c r="R61" s="65"/>
+      <c r="S61" s="66"/>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
       <c r="D62" s="9"/>
-      <c r="E62" s="78"/>
-      <c r="F62" s="79"/>
-      <c r="G62" s="79"/>
-      <c r="H62" s="79"/>
-      <c r="I62" s="80"/>
-      <c r="K62" s="38"/>
-      <c r="L62" s="39"/>
-      <c r="M62" s="39"/>
-      <c r="N62" s="39"/>
-      <c r="O62" s="40"/>
-      <c r="P62" s="78"/>
-      <c r="Q62" s="79"/>
-      <c r="R62" s="79"/>
-      <c r="S62" s="80"/>
+      <c r="E62" s="67"/>
+      <c r="F62" s="68"/>
+      <c r="G62" s="68"/>
+      <c r="H62" s="68"/>
+      <c r="I62" s="69"/>
+      <c r="K62" s="92"/>
+      <c r="L62" s="93"/>
+      <c r="M62" s="93"/>
+      <c r="N62" s="93"/>
+      <c r="O62" s="94"/>
+      <c r="P62" s="67"/>
+      <c r="Q62" s="68"/>
+      <c r="R62" s="68"/>
+      <c r="S62" s="69"/>
     </row>
   </sheetData>
-  <mergeCells count="156">
-    <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:S7"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="I1:S1"/>
-    <mergeCell ref="K2:R2"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="L8:O8"/>
-    <mergeCell ref="P8:S8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="M10:R10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:C13"/>
-    <mergeCell ref="D12:H13"/>
-    <mergeCell ref="I12:M13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="I14:M14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="I15:M15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="I16:M16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="I17:M17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="I18:M18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="I19:M19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="I20:M20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="I21:M21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="I22:M22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="I23:M23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="I24:M24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="I25:M25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="I26:M26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="I27:M27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="I28:M28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="I31:M31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="I32:M32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="I34:M34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="I35:M35"/>
+  <mergeCells count="157">
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="E53:I62"/>
+    <mergeCell ref="K53:O53"/>
+    <mergeCell ref="P53:S62"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="I48:M48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="D49:S49"/>
+    <mergeCell ref="A58:D59"/>
+    <mergeCell ref="K58:O59"/>
+    <mergeCell ref="A51:S51"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="P52:S52"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="K60:O60"/>
+    <mergeCell ref="K61:O62"/>
+    <mergeCell ref="K54:O54"/>
+    <mergeCell ref="A55:D56"/>
+    <mergeCell ref="K55:O56"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="K57:O57"/>
+    <mergeCell ref="A50:S50"/>
+    <mergeCell ref="I43:M43"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="I40:M40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="I41:M41"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="I46:M46"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="I44:M44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="I45:M45"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="D36:H36"/>
     <mergeCell ref="I36:M36"/>
@@ -3487,52 +3389,103 @@
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="D42:H42"/>
     <mergeCell ref="I42:M42"/>
-    <mergeCell ref="A50:S50"/>
-    <mergeCell ref="I43:M43"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="I40:M40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="I41:M41"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="E53:I62"/>
-    <mergeCell ref="K53:O53"/>
-    <mergeCell ref="P53:S62"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="I48:M48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="D49:S49"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="A58:D59"/>
-    <mergeCell ref="K58:O59"/>
-    <mergeCell ref="A51:S51"/>
-    <mergeCell ref="E52:I52"/>
-    <mergeCell ref="P52:S52"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="I46:M46"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="I44:M44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="I45:M45"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="K60:O60"/>
-    <mergeCell ref="K61:O62"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="I33:M33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="I34:M34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="I35:M35"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="I31:M31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="I32:M32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="I27:M27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="I24:M24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="I25:M25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="I26:M26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="I21:M21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="I23:M23"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="I18:M18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="I19:M19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="I20:M20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I15:M15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="I16:M16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="I17:M17"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:C13"/>
+    <mergeCell ref="D12:H13"/>
+    <mergeCell ref="I12:M13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="I14:M14"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="P8:S8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="M10:R10"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:S7"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="I1:S1"/>
+    <mergeCell ref="K2:R2"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:Q3"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="K54:O54"/>
-    <mergeCell ref="A55:D56"/>
-    <mergeCell ref="K55:O56"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="K57:O57"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" r:id="rId1"/>
